--- a/d/2026-09-06_会员有效性分析.xlsx
+++ b/d/2026-09-06_会员有效性分析.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>603</v>
+      </c>
+      <c r="C7" t="n">
         <v>602</v>
-      </c>
-      <c r="C7" t="n">
-        <v>601</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -2666,19 +2666,19 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>华为北京回龙观万科</t>
+          <t>APR成都温江旭辉</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="E76" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -2693,19 +2693,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>华为泉州石狮泰禾广场</t>
+          <t>华为北京回龙观万科</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E77" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>华为福州平潭吾悦</t>
+          <t>华为泉州石狮泰禾广场</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E78" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -2747,19 +2747,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DJI上海漕河泾印象城授权体验店</t>
+          <t>华为福州平潭吾悦</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E79" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -2774,19 +2774,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>华为北京丽泽龙湖</t>
+          <t>DJI上海漕河泾印象城授权体验店</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E80" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>华为北京酒仙桥颐堤港</t>
+          <t>华为北京丽泽龙湖</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>华为北京来福士</t>
+          <t>华为北京酒仙桥颐堤港</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>华为北京怀柔万达</t>
+          <t>华为北京来福士</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E83" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -2882,19 +2882,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DJI北京龙湖房山天街授权体验店</t>
+          <t>华为北京怀柔万达</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E84" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DJI北京石景山万达授权体验店</t>
+          <t>DJI北京龙湖房山天街授权体验店</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E85" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -2936,19 +2936,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>APR北京亦庄龙湖</t>
+          <t>DJI北京石景山万达授权体验店</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E86" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>APR北京东坝万达</t>
+          <t>APR北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E87" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -2990,19 +2990,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DJI北京西北旺万象汇授权体验店</t>
+          <t>APR北京东坝万达</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E88" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -3017,19 +3017,19 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>APR北京同成街华联</t>
+          <t>DJI北京西北旺万象汇授权体验店</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E89" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -3044,19 +3044,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>华为北京大兴大族</t>
+          <t>APR北京同成街华联</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="E90" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>华为北京通州乐堤港</t>
+          <t>华为北京大兴大族</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="E91" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -3098,19 +3098,19 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>APR成都金楠天街</t>
+          <t>华为北京通州乐堤港</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E92" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -3125,19 +3125,19 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DJI北京丰科万达广场授权体验店</t>
+          <t>APR成都金楠天街</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E93" t="n">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -3152,19 +3152,19 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>APR北京望京凯德茂</t>
+          <t>DJI北京丰科万达广场授权体验店</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="E94" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>APR北京石景山万达</t>
+          <t>APR北京望京凯德茂</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E95" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -3206,19 +3206,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DJI北京长楹天街授权体验店</t>
+          <t>APR北京石景山万达</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E96" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DJI北京通州万达授权体验店</t>
+          <t>DJI北京长楹天街授权体验店</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E97" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -3260,19 +3260,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DJI上海徐汇万科广场授权体验店</t>
+          <t>DJI北京通州万达授权体验店</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E98" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -3287,19 +3287,19 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DJI北京昌平超级合生汇授权体验店</t>
+          <t>DJI上海徐汇万科广场授权体验店</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E99" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -3314,19 +3314,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>APR北京长安龙湖</t>
+          <t>DJI北京昌平超级合生汇授权体验店</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E100" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>APR北京西三旗万象汇</t>
+          <t>APR北京长安龙湖</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E101" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -3368,19 +3368,19 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>华为福州大洋晶典</t>
+          <t>APR北京西三旗万象汇</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E102" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -3395,19 +3395,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DJI上海天荟广场授权体验店</t>
+          <t>华为福州大洋晶典</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E103" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -3422,19 +3422,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DJI北京京西大悦城授权体验店</t>
+          <t>DJI上海天荟广场授权体验店</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E104" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -3449,19 +3449,19 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>华为北京房山万科</t>
+          <t>DJI北京京西大悦城授权体验店</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="E105" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>APR成都温江旭辉</t>
+          <t>华为北京房山万科</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="E106" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -5500,7 +5500,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>136****0516</t>
+          <t>185****7000</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>华为北京丰科万达</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5546,7 +5546,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>185****7000</t>
+          <t>136****0516</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>华为北京丰科万达</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5569,7 +5569,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>136****4066</t>
+          <t>138****9886</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5592,7 +5592,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>138****9886</t>
+          <t>183****2985</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>华为北京牡丹园翠微</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>183****2985</t>
+          <t>136****4066</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>华为北京牡丹园翠微</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）带感绿</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6942103183102</t>
+          <t>6942103183133</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -13293,12 +13293,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）带感绿</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6942103183133</t>
+          <t>6942103183102</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -13348,12 +13348,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -19728,12 +19728,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -19838,12 +19838,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -19893,12 +19893,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K124" t="n">
@@ -19948,12 +19948,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K125" t="n">
@@ -20058,12 +20058,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -20113,12 +20113,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K128" t="n">
@@ -20223,12 +20223,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K130" t="n">
@@ -20333,12 +20333,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -20388,12 +20388,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K133" t="n">
@@ -20553,12 +20553,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K136" t="n">
@@ -20608,12 +20608,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -20663,12 +20663,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -20773,12 +20773,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K140" t="n">
@@ -20828,12 +20828,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K141" t="n">
@@ -20883,12 +20883,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -20938,12 +20938,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K143" t="n">
@@ -21103,12 +21103,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K146" t="n">
@@ -21158,12 +21158,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -22588,12 +22588,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
+          <t>nova 15 Ultra SLY-AL00 （12GB+512GB）零度白</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>6942103183133</t>
+          <t>6942103183126</t>
         </is>
       </c>
       <c r="K173" t="n">
@@ -22643,12 +22643,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00 （12GB+512GB）零度白</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>6942103183126</t>
+          <t>6942103183133</t>
         </is>
       </c>
       <c r="K174" t="n">
@@ -22698,12 +22698,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152702</t>
         </is>
       </c>
       <c r="K175" t="n">
@@ -22808,12 +22808,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>6942103152702</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -22918,12 +22918,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K179" t="n">
@@ -22973,12 +22973,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K180" t="n">
@@ -23028,12 +23028,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103152702</t>
         </is>
       </c>
       <c r="K181" t="n">
@@ -23083,12 +23083,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>6942103152702</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -23248,12 +23248,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K185" t="n">
@@ -23303,12 +23303,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K186" t="n">
@@ -23468,12 +23468,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K189" t="n">
@@ -23578,12 +23578,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K191" t="n">
@@ -23688,12 +23688,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K193" t="n">
@@ -23743,12 +23743,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K194" t="n">
@@ -23908,12 +23908,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -23963,12 +23963,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K198" t="n">
@@ -24018,12 +24018,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>6942103188275</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K199" t="n">
@@ -24073,12 +24073,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K200" t="n">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188275</t>
         </is>
       </c>
       <c r="K203" t="n">
@@ -24348,12 +24348,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>6942103188275</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K205" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188275</t>
         </is>
       </c>
       <c r="K206" t="n">
@@ -24568,12 +24568,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K209" t="n">
@@ -24623,12 +24623,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K210" t="n">
@@ -24733,12 +24733,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -24843,12 +24843,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K214" t="n">
@@ -24898,12 +24898,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K215" t="n">
@@ -24953,12 +24953,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K216" t="n">
@@ -25008,12 +25008,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -25063,12 +25063,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K218" t="n">
@@ -25118,12 +25118,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K219" t="n">
@@ -25278,17 +25278,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Hi MateBook</t>
+          <t>MateBook Pro S</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Hi Matebook 14 MNCAC-32(AMD Radeon AMD Ryzen 7 Win11 24GB+1TB)触屏 极夜灰</t>
+          <t>MateBook Pro S MOR-M1(HarmonyOS 24GB+512GB)触屏 仲夏紫</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>6975503504697</t>
+          <t>6942711313007</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -25333,17 +25333,17 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>MateBook Pro S</t>
+          <t>Hi MateBook</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>MateBook Pro S MOR-M1(HarmonyOS 24GB+512GB)触屏 仲夏紫</t>
+          <t>Hi Matebook 14 MNCAC-32(AMD Radeon AMD Ryzen 7 Win11 24GB+1TB)触屏 极夜灰</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>6942711313007</t>
+          <t>6975503504697</t>
         </is>
       </c>
       <c r="K223" t="n">
@@ -25448,12 +25448,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>智选 艾优智能剃须刀 尊享款 H1钛金灰 演示样机</t>
+          <t>EasyFit 2 曜石黑 氟橡胶表带 黑 演示样机</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>YJ6970871389662</t>
+          <t>YJ6941487208418</t>
         </is>
       </c>
       <c r="K225" t="n">
@@ -25503,12 +25503,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>EasyFit 2 曜石黑 氟橡胶表带 黑 演示样机</t>
+          <t>智选 艾优智能剃须刀 尊享款 H1钛金灰 演示样机</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>YJ6941487208418</t>
+          <t>YJ6970871389662</t>
         </is>
       </c>
       <c r="K226" t="n">
@@ -25613,12 +25613,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K228" t="n">
@@ -25668,12 +25668,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K229" t="n">
@@ -25723,12 +25723,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K230" t="n">
@@ -25778,12 +25778,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K231" t="n">
@@ -25833,12 +25833,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K232" t="n">
@@ -25888,12 +25888,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K233" t="n">
@@ -25943,12 +25943,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K234" t="n">
@@ -26108,12 +26108,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K237" t="n">
@@ -26163,12 +26163,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K238" t="n">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K239" t="n">
@@ -26273,12 +26273,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K240" t="n">
@@ -26328,12 +26328,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K241" t="n">
@@ -26493,12 +26493,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Mate 80 VYG-AL30(12GB+512GB) 晨曦金</t>
+          <t>Mate 80 VYG-AL30(12GB+512GB) 云杉绿</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>6942103191657</t>
+          <t>6942103191640</t>
         </is>
       </c>
       <c r="K244" t="n">
@@ -26548,12 +26548,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Mate 80 VYG-AL30(12GB+512GB) 云杉绿</t>
+          <t>Mate 80 VYG-AL30(12GB+512GB) 晨曦金</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>6942103191640</t>
+          <t>6942103191657</t>
         </is>
       </c>
       <c r="K245" t="n">
@@ -27740,12 +27740,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Apple Watch Series 11 (GPS)；46 毫米亮黑色铝金属表壳；黑色运动型表带 - M/L - MEVH4CH/B</t>
+          <t>Apple Watch Series 11 (GPS)；46 毫米玫瑰金色铝金属表壳；淡桃粉色运动型表带 - M/L - MEVU4CH/B</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>195****64757</t>
+          <t>195****64870</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -27811,12 +27811,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Apple Watch Series 11 (GPS)；46 毫米玫瑰金色铝金属表壳；淡桃粉色运动型表带 - M/L - MEVU4CH/B</t>
+          <t>Apple Watch Series 11 (GPS)；46 毫米亮黑色铝金属表壳；黑色运动型表带 - M/L - MEVH4CH/B</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>195****64870</t>
+          <t>195****64757</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -28019,17 +28019,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>鼠标和键盘</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>TOMTOC Defender A14 城市简约手提电脑包</t>
+          <t>ZUER卓耳 四向滚轮三模无线鼠标</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6970412220850</t>
+          <t>6973620631524</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -28090,17 +28090,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>HUNTKEY航嘉 USB-C 4合一 多功能扩展坞 黑色</t>
+          <t>TOMTOC Defender A14 城市简约手提电脑包</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6946333017596</t>
+          <t>6970412220850</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -28161,17 +28161,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>鼠标和键盘</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ZUER卓耳 四向滚轮三模无线鼠标</t>
+          <t>VOKAMO沃咔曼 清薄键盘保护膜</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6973620631524</t>
+          <t>6922329934702</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -28303,17 +28303,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 清薄键盘保护膜</t>
+          <t>HUNTKEY航嘉 USB-C 4合一 多功能扩展坞 黑色</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6922329934702</t>
+          <t>6946333017596</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -28516,17 +28516,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17 冰川减震磁吸肤感保护壳 磨砂透黑</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 雅致黑</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6922329935587</t>
+          <t>6955482539514</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -28587,17 +28587,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 雅致黑</t>
+          <t>VOKAMO 沃咔曼 iPhone 系列 3D 钻石高清三强钢化玻璃膜 黑 iPhone 17/17 Pro</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6955482539514</t>
+          <t>6922329935952</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -28658,17 +28658,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
+          <t>VOKAMO沃咔曼 iPhone 17 冰川减震磁吸肤感保护壳 磨砂透黑</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6955482542736</t>
+          <t>6922329935587</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -28729,17 +28729,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
+          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6922329935921</t>
+          <t>195****10144</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -28800,17 +28800,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>VOKAMO 沃咔曼 iPhone 系列 3D 钻石高清三强钢化玻璃膜 黑 iPhone 17/17 Pro</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6922329935952</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -28871,17 +28871,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
+          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>195****10144</t>
+          <t>6922329935921</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -28947,12 +28947,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6955482542736</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -29013,17 +29013,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>RECCI锐思 REP W59 铂爵 ANC 头戴式无线耳机</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>6955482533109</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -29084,17 +29084,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>iPad Pro</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>11 英寸 iPad Pro 无线局域网机型 256GB 配标准玻璃面板 - 银色</t>
+          <t>RECCI锐思 REP W59 铂爵 ANC 头戴式无线耳机</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>195****95549</t>
+          <t>6955482533109</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -29155,17 +29155,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>iPad Pro</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
+          <t>11 英寸 iPad Pro 无线局域网机型 256GB 配标准玻璃面板 - 银色</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6927123805548</t>
+          <t>195****95549</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -29226,17 +29226,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
+          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>6955482542989</t>
+          <t>6927123805548</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -29297,17 +29297,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>MOCOLL摩可 iPad Pro 11英寸 铂金系列 高清钢化玻璃膜</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6937045847984</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -29368,17 +29368,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 iPad Pro 11英寸 铂金系列 高清钢化玻璃膜</t>
+          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>6937045847984</t>
+          <t>6955482542989</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -29515,12 +29515,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
+          <t>VOKAMO沃咔曼 iPad 系列魔幻旋转防刮保护套</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6937045874478</t>
+          <t>6922329935303</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -29652,17 +29652,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
+          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>6941876245338</t>
+          <t>6937045874478</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -29723,17 +29723,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPad 系列魔幻旋转防刮保护套</t>
+          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>6922329935303</t>
+          <t>6941876245338</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -29936,17 +29936,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 512GB 深蓝色 - MG084CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>195****41165</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -30007,17 +30007,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>iPhone 17 Pro Max 512GB 深蓝色 - MG084CH/A</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****41165</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -30367,12 +30367,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 太阳橙</t>
+          <t>ZGA iPhone 17 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4894222083837</t>
+          <t>6927123810382</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -30438,12 +30438,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 防偷窥防静电二强钢化膜 黑色</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>6927123810382</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -30580,12 +30580,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 太阳橙</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>4894222083837</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -30717,17 +30717,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>FPV</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（中号）</t>
+          <t>DJI Neo 2（仅飞行器）</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>6937224129511</t>
+          <t>6937224131767</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -30788,17 +30788,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>FPV</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>DJI Neo 2（仅飞行器）</t>
+          <t>DJI 无纺布购物袋（中号）</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>6937224131767</t>
+          <t>6937224129511</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -34042,17 +34042,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -34118,12 +34118,12 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 黑色 iPhone 17</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>6927123810429</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -34255,17 +34255,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 黑色 iPhone 17</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>6927123810429</t>
         </is>
       </c>
       <c r="L97" t="n">
@@ -34326,17 +34326,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L98" t="n">
@@ -34397,17 +34397,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -34965,17 +34965,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>6922329936577</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L107" t="n">
@@ -35320,17 +35320,17 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>6922329936577</t>
         </is>
       </c>
       <c r="L112" t="n">
@@ -35391,17 +35391,17 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -35746,17 +35746,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>6927123810559</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -35817,17 +35817,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -35893,12 +35893,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>6927123810559</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -35959,17 +35959,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -36035,12 +36035,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>6955482539477</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -36101,17 +36101,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -36172,17 +36172,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>6955482539477</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -36243,17 +36243,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -36314,17 +36314,17 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -36461,12 +36461,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -36603,12 +36603,12 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6955482539477</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -36674,12 +36674,12 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -36740,17 +36740,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -36811,17 +36811,17 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -36882,17 +36882,17 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>6927123810559</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -37029,12 +37029,12 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>6927123810559</t>
         </is>
       </c>
       <c r="L136" t="n">
@@ -37095,17 +37095,17 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>6955482539477</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -37739,12 +37739,12 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>11 英寸 iPad GPS 128GB/蓝色-MD4A4CH/A</t>
+          <t>11 英寸 iPad GPS 128GB/粉色-MD4E4CH/A</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>195****86379</t>
+          <t>195****86836</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -37870,23 +37870,20 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>iPad基础版</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>NO1BOX IPhone 17 Pro Max 蜡笔小新春日部防卫队保护壳 出发啦</t>
+          <t>11 英寸 iPad GPS 128GB/蓝色-MD4A4CH/A</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>6923517323407</t>
+          <t>195****86379</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>1</v>
-      </c>
-      <c r="M148" t="n">
         <v>1</v>
       </c>
       <c r="N148" t="n">
@@ -37941,20 +37938,23 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>iPad基础版</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>11 英寸 iPad GPS 128GB/粉色-MD4E4CH/A</t>
+          <t>NO1BOX IPhone 17 Pro Max 蜡笔小新春日部防卫队保护壳 出发啦</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>195****86836</t>
+          <t>6923517323407</t>
         </is>
       </c>
       <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
         <v>1</v>
       </c>
       <c r="N149" t="n">
@@ -38085,12 +38085,12 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>COMMA珂玛 iPad 灵动保护皮套带笔槽  11 英寸 iPad (A16) 动物派对</t>
+          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>6942297127241</t>
+          <t>6942297127005</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -38156,12 +38156,12 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPad 高清保护膜</t>
+          <t>COMMA珂玛 iPad 灵动保护皮套带笔槽  11 英寸 iPad (A16) 动物派对</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>6974623613036</t>
+          <t>6942297127241</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -38227,12 +38227,12 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
+          <t>RICHIC锐壳 iPad 高清保护膜</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>6942297127005</t>
+          <t>6974623613036</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -38369,12 +38369,12 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
+          <t>RICHIC锐壳 iPad 高清保护膜</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>6942297127012</t>
+          <t>6974623613036</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -38440,12 +38440,12 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPad 高清保护膜</t>
+          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>6974623613036</t>
+          <t>6942297127012</t>
         </is>
       </c>
       <c r="L156" t="n">
@@ -38577,17 +38577,17 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>音乐</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
+          <t>AirPods 4 (支持主动降噪)-MXP93CH/A</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>6941876245437</t>
+          <t>195****89550</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -38648,17 +38648,17 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>音乐</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>AirPods 4 (支持主动降噪)-MXP93CH/A</t>
+          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>195****89550</t>
+          <t>6941876245437</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -41690,17 +41690,17 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>保护</t>
+          <t>外设</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>仁清 UV高清晶钻膜 180GJZ-01G9是（S码）</t>
+          <t>迈多多 DY24 10000mAh移动电源 白色</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>6941402717384</t>
+          <t>6927123806422</t>
         </is>
       </c>
       <c r="L202" t="n">
@@ -41761,17 +41761,17 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>外设</t>
+          <t>保护</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>迈多多 DY24 10000mAh移动电源 白色</t>
+          <t>仁清 UV高清晶钻膜 180GJZ-01G9是（S码）</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>6927123806422</t>
+          <t>6941402717384</t>
         </is>
       </c>
       <c r="L203" t="n">
@@ -42258,17 +42258,17 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 灰色 iPhone 17</t>
+          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>6927123810436</t>
+          <t>195****10144</t>
         </is>
       </c>
       <c r="L210" t="n">
@@ -42329,17 +42329,17 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L211" t="n">
@@ -42405,12 +42405,12 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 灰色 iPhone 17</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6927123810436</t>
         </is>
       </c>
       <c r="L212" t="n">
@@ -42476,12 +42476,12 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L213" t="n">
@@ -42542,17 +42542,17 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>195****10144</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L214" t="n">
@@ -42618,12 +42618,12 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L215" t="n">
@@ -42689,12 +42689,12 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L216" t="n">
@@ -43110,17 +43110,17 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L222" t="n">
@@ -43181,17 +43181,17 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L223" t="n">
@@ -43252,17 +43252,17 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L224" t="n">
@@ -43536,17 +43536,17 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 橙色</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6928288500057</t>
         </is>
       </c>
       <c r="L228" t="n">
@@ -43607,17 +43607,17 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L229" t="n">
@@ -43678,17 +43678,17 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>6941876245437</t>
         </is>
       </c>
       <c r="L230" t="n">
@@ -43749,17 +43749,17 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 橙色</t>
+          <t>RICHIC锐壳 氮化镓三口充电器 65W</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>6928288500057</t>
+          <t>6974623613029</t>
         </is>
       </c>
       <c r="L231" t="n">
@@ -43820,17 +43820,17 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 氮化镓三口充电器 65W</t>
+          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 黑色</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>6974623613029</t>
+          <t>4894222083820</t>
         </is>
       </c>
       <c r="L232" t="n">
@@ -43891,17 +43891,17 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>6941876245437</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L233" t="n">
@@ -43967,12 +43967,12 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 黑色</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>4894222083820</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L234" t="n">
@@ -44388,23 +44388,20 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Pocket</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 1年版（Osmo Pocket 4P）中国版</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>6937224151062</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L240" t="n">
-        <v>1</v>
-      </c>
-      <c r="M240" t="n">
         <v>1</v>
       </c>
       <c r="N240" t="n">
@@ -44464,12 +44461,12 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 1年版（Osmo Pocket 4P）中国版</t>
+          <t>Osmo 迷你三脚架</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>6937224151062</t>
+          <t>6941565969811</t>
         </is>
       </c>
       <c r="L241" t="n">
@@ -44532,12 +44529,12 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Osmo Pocket 4P 标准套装</t>
+          <t>DJI Care 随心换 1年版（Osmo Pocket 4P）中国版</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>6937224148321</t>
+          <t>6937224151062</t>
         </is>
       </c>
       <c r="L242" t="n">
@@ -44595,20 +44592,23 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Pocket</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>Osmo Pocket 4P 标准套装</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6937224148321</t>
         </is>
       </c>
       <c r="L243" t="n">
+        <v>1</v>
+      </c>
+      <c r="M243" t="n">
         <v>1</v>
       </c>
       <c r="N243" t="n">
@@ -44668,12 +44668,12 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Osmo Pocket 4P 标准套装</t>
+          <t>DJI Care 随心换 1年版（Osmo Pocket 4P）中国版</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>6937224148321</t>
+          <t>6937224151062</t>
         </is>
       </c>
       <c r="L244" t="n">
@@ -44739,12 +44739,12 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Osmo 迷你三脚架</t>
+          <t>Osmo Pocket 4P 标准套装</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>6941565969811</t>
+          <t>6937224148321</t>
         </is>
       </c>
       <c r="L245" t="n">
@@ -45938,17 +45938,17 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Osmo Action 6 多功能扩展框</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>6937224142985</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L262" t="n">
@@ -46009,17 +46009,17 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>Osmo Action 6 多功能扩展框</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6937224142985</t>
         </is>
       </c>
       <c r="L263" t="n">
@@ -46795,12 +46795,12 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 黑色</t>
+          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 白色</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>6941487218028</t>
+          <t>6941487218011</t>
         </is>
       </c>
       <c r="L274" t="n">
@@ -46866,12 +46866,12 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 白色</t>
+          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 黑色</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>6941487218011</t>
+          <t>6941487218028</t>
         </is>
       </c>
       <c r="L275" t="n">
@@ -48210,12 +48210,12 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L294" t="n">
@@ -48281,12 +48281,12 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L295" t="n">
@@ -48489,17 +48489,17 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>表带</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>COMMA珂玛  盾威系列全屏 Apple Watch 46mm 保护膜 V3</t>
+          <t>SWITCHEASY Apple Watch 系列 Mesh 不锈钢磁扣表带</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>6942297146426</t>
+          <t>6977503191334</t>
         </is>
       </c>
       <c r="L298" t="n">
@@ -48560,17 +48560,17 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>表带</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>SWITCHEASY Apple Watch 系列 Mesh 不锈钢磁扣表带</t>
+          <t>COMMA珂玛  盾威系列全屏 Apple Watch 46mm 保护膜 V3</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>6977503191334</t>
+          <t>6942297146426</t>
         </is>
       </c>
       <c r="L299" t="n">
@@ -48636,12 +48636,12 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>ZGA iPhone 17e 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6927123814069</t>
         </is>
       </c>
       <c r="L300" t="n">
@@ -48778,12 +48778,12 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17e 二强防静电高清钢化膜 透明</t>
+          <t>ZGA 明透磁吸 保护壳 透明 iPhone 16e</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>6927123814069</t>
+          <t>6927123805746</t>
         </is>
       </c>
       <c r="L302" t="n">
@@ -48849,12 +48849,12 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>ZGA 明透磁吸 保护壳 透明 iPhone 16e</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>6927123805746</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L303" t="n">
@@ -49341,17 +49341,17 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
+          <t>VOKAMO沃咔曼 iPad Air 魔幻旋转防刮保护套</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>6941876245338</t>
+          <t>6922329934283</t>
         </is>
       </c>
       <c r="L310" t="n">
@@ -49412,17 +49412,17 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPad 高清保护膜</t>
+          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>6974623613036</t>
+          <t>6941876245338</t>
         </is>
       </c>
       <c r="L311" t="n">
@@ -49559,12 +49559,12 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPad Air 魔幻旋转防刮保护套</t>
+          <t>RICHIC锐壳 iPad 高清保护膜</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>6922329934283</t>
+          <t>6974623613036</t>
         </is>
       </c>
       <c r="L313" t="n">
@@ -49767,17 +49767,17 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L316" t="n">
@@ -49909,17 +49909,17 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L318" t="n">
@@ -50329,17 +50329,17 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>Osmo 70 厘米隐形自拍杆</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>6937224111165</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L324" t="n">
@@ -50400,17 +50400,17 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>Osmo 70 厘米隐形自拍杆</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6937224111165</t>
         </is>
       </c>
       <c r="L325" t="n">
@@ -54565,17 +54565,17 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>运营商卡号</t>
+          <t>MatePad pro</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>橙分期团购合约-129-24（终端直降1170）</t>
+          <t>MatePad Pro 12.2寸 MRO-W00(12GB+512GB) 砚黑</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>811094496</t>
+          <t>6942103130816</t>
         </is>
       </c>
       <c r="L384" t="n">
@@ -54636,17 +54636,17 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>MatePad pro</t>
+          <t>运营商卡号</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>MatePad Pro 12.2寸 MRO-W00(12GB+512GB) 砚黑</t>
+          <t>橙分期团购合约-129-24（终端直降1170）</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>6942103130816</t>
+          <t>811094496</t>
         </is>
       </c>
       <c r="L385" t="n">
@@ -55842,12 +55842,12 @@
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>ZGA iPad 流派系列 Y 折 保护皮套</t>
+          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>6927123806750</t>
+          <t>6937045874478</t>
         </is>
       </c>
       <c r="L402" t="n">
@@ -55913,12 +55913,12 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
+          <t>ZGA iPad 流派系列 Y 折 保护皮套</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>6937045874478</t>
+          <t>6927123806750</t>
         </is>
       </c>
       <c r="L403" t="n">
@@ -55979,17 +55979,17 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>iPad Pro</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>SENNHEISER森海塞尔 ACCENTUM 无线蓝牙头戴主动降噪耳机 白色</t>
+          <t>11 英寸 iPad Pro 无线局域网 + 蜂窝网络机型 256GB 配标准玻璃面板 - 深空黑色 - ME6E4CH/A</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>4260752330572</t>
+          <t>195****03541</t>
         </is>
       </c>
       <c r="L404" t="n">
@@ -56050,17 +56050,17 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>iPad Pro</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>11 英寸 iPad Pro 无线局域网 + 蜂窝网络机型 256GB 配标准玻璃面板 - 深空黑色 - ME6E4CH/A</t>
+          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>195****03541</t>
+          <t>6955482542989</t>
         </is>
       </c>
       <c r="L405" t="n">
@@ -56121,17 +56121,17 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
+          <t>HUNTKEY航嘉 USB-C 4合一 多功能扩展坞 黑色</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>6955482542989</t>
+          <t>6946333017596</t>
         </is>
       </c>
       <c r="L406" t="n">
@@ -56192,17 +56192,17 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>HUNTKEY航嘉 USB-C 4合一 多功能扩展坞 黑色</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>6946333017596</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L407" t="n">
@@ -56263,17 +56263,17 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>SENNHEISER森海塞尔 ACCENTUM 无线蓝牙头戴主动降噪耳机 白色</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>4260752330572</t>
         </is>
       </c>
       <c r="L408" t="n">
@@ -57115,17 +57115,17 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>COMMA珂玛  盾威系列全屏 Apple Watch 46mm 保护膜 V3</t>
+          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>6942297146426</t>
+          <t>6955482539477</t>
         </is>
       </c>
       <c r="L420" t="n">
@@ -57186,17 +57186,17 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>表带</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>ZGA 海洋硅胶表带 Watch 42/44/45/49mm 白色</t>
+          <t>COMMA珂玛  盾威系列全屏 Apple Watch 46mm 保护膜 V3</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>6927123804718</t>
+          <t>6942297146426</t>
         </is>
       </c>
       <c r="L421" t="n">
@@ -57257,17 +57257,17 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>表带</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
+          <t>ZGA 海洋硅胶表带 Watch 42/44/45/49mm 白色</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>6955482539477</t>
+          <t>6927123804718</t>
         </is>
       </c>
       <c r="L422" t="n">
@@ -57825,17 +57825,17 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
+          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>6955482542989</t>
+          <t>6927123805432</t>
         </is>
       </c>
       <c r="L430" t="n">
@@ -57967,17 +57967,17 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
+          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>6927123805432</t>
+          <t>6955482542989</t>
         </is>
       </c>
       <c r="L432" t="n">
@@ -58114,12 +58114,12 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无尘舱高清钢化膜 透明 iPhone 17 Pro</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>6927123810900</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L434" t="n">
@@ -58185,12 +58185,12 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 无尘舱高清钢化膜 透明 iPhone 17 Pro</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6927123810900</t>
         </is>
       </c>
       <c r="L435" t="n">
@@ -58398,12 +58398,12 @@
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>LEMANCHUANGYAN乐漫创衍 iPhone 17 Pro Max 迪士尼莓果草莓熊磁吸保护壳 粉色</t>
+          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>6975749267219</t>
+          <t>6927123810405</t>
         </is>
       </c>
       <c r="L438" t="n">
@@ -58464,17 +58464,17 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>6927123810405</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L439" t="n">
@@ -58535,17 +58535,17 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 白色</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>6928288555361</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L440" t="n">
@@ -58606,17 +58606,17 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>RICHIC锐壳 iPhone 17 Pro Max 透明磨砂保护壳 透明</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6978880670153</t>
         </is>
       </c>
       <c r="L441" t="n">
@@ -58677,17 +58677,17 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 白色</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6928288555361</t>
         </is>
       </c>
       <c r="L442" t="n">
@@ -58753,12 +58753,12 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPhone 17 Pro Max 透明磨砂保护壳 透明</t>
+          <t>LEMANCHUANGYAN乐漫创衍 iPhone 17 Pro Max 迪士尼莓果草莓熊磁吸保护壳 粉色</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>6978880670153</t>
+          <t>6975749267219</t>
         </is>
       </c>
       <c r="L443" t="n">
@@ -59245,17 +59245,17 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>SOUNDCORE声阔 Life Q45 无线蓝牙耳机头戴式降噪耳机</t>
+          <t>iPhone 17 Pro Max 256GB 银色 - MG034CH/A</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>6940268897810</t>
+          <t>195****41110</t>
         </is>
       </c>
       <c r="L450" t="n">
@@ -59316,17 +59316,17 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>SOUNDCORE声阔 Life Q45 无线蓝牙耳机头戴式降噪耳机</t>
         </is>
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>6940268897810</t>
         </is>
       </c>
       <c r="L451" t="n">
@@ -59387,17 +59387,17 @@
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 银色 - MG034CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>195****41110</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L452" t="n">
@@ -66049,17 +66049,17 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>iPhone 17 Pro</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>iPhone 17 Pro 512GB 星宇橙色 - MG8X4CH/A</t>
         </is>
       </c>
       <c r="K546" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>195****28906</t>
         </is>
       </c>
       <c r="L546" t="n">
@@ -66125,12 +66125,12 @@
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 灰色 iPhone 17 Pro</t>
         </is>
       </c>
       <c r="K547" t="inlineStr">
         <is>
-          <t>6927123810375</t>
+          <t>6927123810498</t>
         </is>
       </c>
       <c r="L547" t="n">
@@ -66191,17 +66191,17 @@
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro 512GB 星宇橙色 - MG8X4CH/A</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K548" t="inlineStr">
         <is>
-          <t>195****28906</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L548" t="n">
@@ -66267,12 +66267,12 @@
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 灰色 iPhone 17 Pro</t>
+          <t>ZGA iPhone 17 Pro 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K549" t="inlineStr">
         <is>
-          <t>6927123810498</t>
+          <t>6927123810375</t>
         </is>
       </c>
       <c r="L549" t="n">
@@ -66338,12 +66338,12 @@
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K550" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L550" t="n">
@@ -66404,17 +66404,17 @@
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>AppleCare Services for iPhone 17 Pro - SY7N2CH/A</t>
         </is>
       </c>
       <c r="K551" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****10120</t>
         </is>
       </c>
       <c r="L551" t="n">
@@ -66475,17 +66475,17 @@
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>存储</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>LEXAR雷克沙 Professional Go 手机固态硬盘 银色 1T</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K552" t="inlineStr">
         <is>
-          <t>6977105652165</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L552" t="n">
@@ -66617,17 +66617,17 @@
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>存储</t>
         </is>
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>LEXAR雷克沙 Professional Go 手机固态硬盘 银色 1T</t>
         </is>
       </c>
       <c r="K554" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>6977105652165</t>
         </is>
       </c>
       <c r="L554" t="n">
@@ -66688,17 +66688,17 @@
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro - SY7N2CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K555" t="inlineStr">
         <is>
-          <t>195****10120</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L555" t="n">
@@ -66759,17 +66759,17 @@
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>iPhone 17 Pro</t>
         </is>
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>iPhone 17 Pro 512GB 星宇橙色 - MG8X4CH/A</t>
         </is>
       </c>
       <c r="K556" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****28906</t>
         </is>
       </c>
       <c r="L556" t="n">
@@ -66830,17 +66830,17 @@
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro 512GB 星宇橙色 - MG8X4CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K557" t="inlineStr">
         <is>
-          <t>195****28906</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L557" t="n">
@@ -66972,17 +66972,17 @@
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
+          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
         </is>
       </c>
       <c r="K559" t="inlineStr">
         <is>
-          <t>6927123805432</t>
+          <t>6955482542989</t>
         </is>
       </c>
       <c r="L559" t="n">
@@ -67043,17 +67043,17 @@
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
+          <t>MOCOLL摩可 iPad Air 11英寸 铂金系列 高清钢化玻璃膜</t>
         </is>
       </c>
       <c r="K560" t="inlineStr">
         <is>
-          <t>6955482542989</t>
+          <t>6937045848004</t>
         </is>
       </c>
       <c r="L560" t="n">
@@ -67114,17 +67114,17 @@
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>RECCI锐思 REP W59 铂爵 ANC 头戴式无线耳机</t>
         </is>
       </c>
       <c r="K561" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6955482533109</t>
         </is>
       </c>
       <c r="L561" t="n">
@@ -67185,17 +67185,17 @@
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>RECCI锐思 REP W59 铂爵 ANC 头戴式无线耳机</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K562" t="inlineStr">
         <is>
-          <t>6955482533109</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L562" t="n">
@@ -67261,12 +67261,12 @@
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 iPad Air 11英寸 铂金系列 高清钢化玻璃膜</t>
+          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K563" t="inlineStr">
         <is>
-          <t>6937045848004</t>
+          <t>6927123805432</t>
         </is>
       </c>
       <c r="L563" t="n">
@@ -67824,17 +67824,17 @@
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro 防偷窥防静电二强钢化膜 黑色</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
         </is>
       </c>
       <c r="K571" t="inlineStr">
         <is>
-          <t>6927123810351</t>
+          <t>6922329936577</t>
         </is>
       </c>
       <c r="L571" t="n">
@@ -67895,17 +67895,17 @@
       </c>
       <c r="I572" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J572" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K572" t="inlineStr">
         <is>
-          <t>6922329936577</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L572" t="n">
@@ -68042,12 +68042,12 @@
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>ZGA iPhone 17 Pro 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K574" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>6927123810351</t>
         </is>
       </c>
       <c r="L574" t="n">
@@ -68823,12 +68823,12 @@
       </c>
       <c r="J585" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPhone 17 高清保护膜 透明</t>
+          <t>LEMANCHUANGYAN乐漫创衍 iPhone 17 迪士尼 100 周年米奇保护壳 金色</t>
         </is>
       </c>
       <c r="K585" t="inlineStr">
         <is>
-          <t>6978880670016</t>
+          <t>6975749267066</t>
         </is>
       </c>
       <c r="L585" t="n">
@@ -68889,17 +68889,17 @@
       </c>
       <c r="I586" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J586" t="inlineStr">
         <is>
-          <t>LEMANCHUANGYAN乐漫创衍 iPhone 17 迪士尼 100 周年米奇保护壳 金色</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K586" t="inlineStr">
         <is>
-          <t>6975749267066</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L586" t="n">
@@ -69031,17 +69031,17 @@
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J588" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>RICHIC锐壳 iPhone 17 高清保护膜 透明</t>
         </is>
       </c>
       <c r="K588" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6978880670016</t>
         </is>
       </c>
       <c r="L588" t="n">
@@ -69244,17 +69244,17 @@
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J591" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K591" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L591" t="n">
@@ -69315,17 +69315,17 @@
       </c>
       <c r="I592" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
+          <t>HUNTKEY航嘉 5A 2.0m USB-C 数据线 100W</t>
         </is>
       </c>
       <c r="K592" t="inlineStr">
         <is>
-          <t>6927123810405</t>
+          <t>6946333016698</t>
         </is>
       </c>
       <c r="L592" t="n">
@@ -69386,17 +69386,17 @@
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>HUNTKEY航嘉 5A 2.0m USB-C 数据线 100W</t>
+          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 太阳橙</t>
         </is>
       </c>
       <c r="K593" t="inlineStr">
         <is>
-          <t>6946333016698</t>
+          <t>4894222083837</t>
         </is>
       </c>
       <c r="L593" t="n">
@@ -69457,17 +69457,17 @@
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 橙色</t>
         </is>
       </c>
       <c r="K594" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>6928288500057</t>
         </is>
       </c>
       <c r="L594" t="n">
@@ -69533,12 +69533,12 @@
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 太阳橙</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K595" t="inlineStr">
         <is>
-          <t>4894222083837</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L595" t="n">
@@ -69599,17 +69599,17 @@
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 橙色</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K596" t="inlineStr">
         <is>
-          <t>6928288500057</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L596" t="n">
@@ -69670,17 +69670,17 @@
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K597" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6927123810405</t>
         </is>
       </c>
       <c r="L597" t="n">
@@ -69812,17 +69812,17 @@
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>iPhone 17 Pro</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>MAGICPIX魔图极秀 iPhone 17 系列摄影课程 - 用 iPhone 拍照片</t>
+          <t>iPhone 17 Pro 256GB 银色 - MG8T4CH/A</t>
         </is>
       </c>
       <c r="K599" t="inlineStr">
         <is>
-          <t>XMPZ202612189</t>
+          <t>195****28869</t>
         </is>
       </c>
       <c r="L599" t="n">
@@ -69883,17 +69883,17 @@
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>MAGICPIX魔图极秀 iPhone 17 系列摄影课程 - 用 iPhone 拍照片</t>
         </is>
       </c>
       <c r="K600" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>XMPZ202612189</t>
         </is>
       </c>
       <c r="L600" t="n">
@@ -69954,17 +69954,17 @@
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro 256GB 银色 - MG8T4CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K601" t="inlineStr">
         <is>
-          <t>195****28869</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L601" t="n">
@@ -70527,18 +70527,15 @@
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 2年版（Osmo Action 4）中国版</t>
+          <t>Osmo Action 4 标准套装</t>
         </is>
       </c>
       <c r="K609" t="inlineStr">
         <is>
-          <t>6941565963765</t>
+          <t>6941565965073</t>
         </is>
       </c>
       <c r="L609" t="n">
-        <v>1</v>
-      </c>
-      <c r="M609" t="n">
         <v>1</v>
       </c>
       <c r="N609" t="n">
@@ -70598,15 +70595,18 @@
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>Osmo Action 4 标准套装</t>
+          <t>DJI Care 随心换 2年版（Osmo Action 4）中国版</t>
         </is>
       </c>
       <c r="K610" t="inlineStr">
         <is>
-          <t>6941565965073</t>
+          <t>6941565963765</t>
         </is>
       </c>
       <c r="L610" t="n">
+        <v>1</v>
+      </c>
+      <c r="M610" t="n">
         <v>1</v>
       </c>
       <c r="N610" t="n">
@@ -70942,23 +70942,20 @@
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>Osmo Action 4 全能套装</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K615" t="inlineStr">
         <is>
-          <t>6941565965080</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L615" t="n">
-        <v>1</v>
-      </c>
-      <c r="M615" t="n">
         <v>1</v>
       </c>
       <c r="N615" t="n">
@@ -71013,20 +71010,23 @@
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>Osmo Action 4 全能套装</t>
         </is>
       </c>
       <c r="K616" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6941565965080</t>
         </is>
       </c>
       <c r="L616" t="n">
+        <v>1</v>
+      </c>
+      <c r="M616" t="n">
         <v>1</v>
       </c>
       <c r="N616" t="n">
@@ -73586,17 +73586,17 @@
       </c>
       <c r="I653" t="inlineStr">
         <is>
-          <t>Pocket</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>Osmo Pocket 4</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>6937224133099</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L653" t="n">
@@ -73657,17 +73657,17 @@
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Pocket</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>Osmo Pocket 4</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6937224133099</t>
         </is>
       </c>
       <c r="L654" t="n">
@@ -73938,17 +73938,17 @@
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>Nano</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>Osmo Nano 随行套装</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
         <is>
-          <t>6937224157705</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L658" t="n">
@@ -74009,17 +74009,17 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Nano</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>Osmo Nano 随行套装</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6937224157705</t>
         </is>
       </c>
       <c r="L659" t="n">
@@ -74080,17 +74080,17 @@
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Nano</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>DJI Care 随心换 1年版（Osmo Nano）中国版</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6937224116146</t>
         </is>
       </c>
       <c r="L660" t="n">
@@ -74151,17 +74151,17 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>Nano</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 1年版（Osmo Nano）中国版</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
         <is>
-          <t>6937224116146</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L661" t="n">
@@ -76671,17 +76671,17 @@
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>Mate 80</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>礼品-定制-憨憨2.0盲盒-会员专属</t>
+          <t>Mate 80 Pro SGT-AL50(12GB+512GB) 曜石黑</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>A0800911</t>
+          <t>6942103178986</t>
         </is>
       </c>
       <c r="L697" t="n">
@@ -76742,17 +76742,17 @@
       </c>
       <c r="I698" t="inlineStr">
         <is>
-          <t>Mate 80</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>Mate 80 Pro SGT-AL50(12GB+512GB) 曜石黑</t>
+          <t>礼品-定制-憨憨2.0盲盒-会员专属</t>
         </is>
       </c>
       <c r="K698" t="inlineStr">
         <is>
-          <t>6942103178986</t>
+          <t>A0800911</t>
         </is>
       </c>
       <c r="L698" t="n">
@@ -76813,23 +76813,20 @@
       </c>
       <c r="I699" t="inlineStr">
         <is>
-          <t>Pura 80</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>Pura 80 Ultra LMR-AL10 16GB+512GB 鎏光金</t>
+          <t>礼品-定制-沙发嘿嘿摆件2</t>
         </is>
       </c>
       <c r="K699" t="inlineStr">
         <is>
-          <t>6942103162756</t>
+          <t>A0800813</t>
         </is>
       </c>
       <c r="L699" t="n">
-        <v>1</v>
-      </c>
-      <c r="M699" t="n">
         <v>1</v>
       </c>
       <c r="N699" t="n">
@@ -76884,20 +76881,23 @@
       </c>
       <c r="I700" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>Pura 80</t>
         </is>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>礼品-定制-沙发嘿嘿摆件2</t>
+          <t>Pura 80 Ultra LMR-AL10 16GB+512GB 鎏光金</t>
         </is>
       </c>
       <c r="K700" t="inlineStr">
         <is>
-          <t>A0800813</t>
+          <t>6942103162756</t>
         </is>
       </c>
       <c r="L700" t="n">
+        <v>1</v>
+      </c>
+      <c r="M700" t="n">
         <v>1</v>
       </c>
       <c r="N700" t="n">
